--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B5" t="n">
-        <v>80090</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R5" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,6 +1038,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,32 +1069,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>80090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R6" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1135,11 +1140,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R7" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,6 +1237,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1274,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1298,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R8" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B10" t="n">
-        <v>80090</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R10" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,6 +1538,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,32 +1569,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>80090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R11" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1635,11 +1640,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>80090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R5" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,11 +1038,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B6" t="n">
-        <v>80090</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1104,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R6" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1140,6 +1135,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R7" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,11 +1237,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,10 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B8" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R8" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1334,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920255</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>129920247</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B5" t="n">
-        <v>80090</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R5" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,6 +1038,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,32 +1069,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>80093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R6" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1135,11 +1140,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R7" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,6 +1237,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1274,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1298,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R8" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1368,7 +1368,7 @@
         <v>129920254</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129920261</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129920248</v>
       </c>
       <c r="B11" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>129920250</v>
       </c>
       <c r="B12" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129920258</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>129920252</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R7" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,6 +1237,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1274,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1298,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R8" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B5" t="n">
-        <v>80189</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R5" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,6 +1038,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,32 +1069,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R6" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1135,11 +1140,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R7" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,11 +1237,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,10 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R8" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1334,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B5" t="n">
-        <v>80189</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R5" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,6 +1038,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,32 +1069,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R6" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1135,11 +1140,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1169,7 +1169,7 @@
         <v>129920246</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129920248</v>
       </c>
       <c r="B11" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>129920250</v>
       </c>
       <c r="B12" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920255</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>129920247</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>80218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R5" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,11 +1038,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1104,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R6" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1140,6 +1135,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B7" t="n">
-        <v>91731</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R7" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,6 +1237,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>91757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1274,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1298,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R8" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1368,7 +1368,7 @@
         <v>129920254</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129920261</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129920248</v>
       </c>
       <c r="B11" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>129920250</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129920258</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>129920252</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B10" t="n">
-        <v>57852</v>
+        <v>80218</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R10" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,11 +1538,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1569,32 +1564,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B11" t="n">
-        <v>80218</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1604,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R11" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,6 +1635,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>91759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R7" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,11 +1237,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,10 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B8" t="n">
-        <v>91758</v>
+        <v>57852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R8" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1334,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B10" t="n">
-        <v>80218</v>
+        <v>57852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R10" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,6 +1538,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,32 +1569,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>80218</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R11" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1635,11 +1640,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920255</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>129920247</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>129920249</v>
       </c>
       <c r="B5" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>129920256</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>129920246</v>
       </c>
       <c r="B7" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>129920260</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129920254</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B10" t="n">
-        <v>57852</v>
+        <v>80220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R10" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,11 +1538,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1569,32 +1564,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B11" t="n">
-        <v>80218</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1604,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R11" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,6 +1635,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,7 +1669,7 @@
         <v>129920250</v>
       </c>
       <c r="B12" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129920258</v>
       </c>
       <c r="B13" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>129920252</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R7" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,6 +1237,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>91761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1274,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1298,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R8" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R7" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,11 +1237,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,10 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B8" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R8" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1334,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B10" t="n">
-        <v>80220</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R10" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,6 +1538,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,32 +1569,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>80220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R11" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1635,11 +1640,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R7" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,6 +1237,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>91761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1274,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1298,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R8" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1334,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>80220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R10" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,11 +1538,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1569,32 +1564,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B11" t="n">
-        <v>80220</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1604,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R11" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,6 +1635,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920255</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>129920247</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B5" t="n">
-        <v>80220</v>
+        <v>57862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R5" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,6 +1038,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,32 +1069,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>80228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R6" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1135,11 +1140,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1169,7 +1169,7 @@
         <v>129920260</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129920254</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B10" t="n">
-        <v>80220</v>
+        <v>57862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R10" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,6 +1538,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,32 +1569,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>80228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R11" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1635,11 +1640,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,7 +1669,7 @@
         <v>129920250</v>
       </c>
       <c r="B12" t="n">
-        <v>80220</v>
+        <v>80228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129920258</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>129920252</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920255</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>129920247</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>129920256</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129920249</v>
       </c>
       <c r="B6" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>129920260</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>129920246</v>
       </c>
       <c r="B8" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129920254</v>
       </c>
       <c r="B9" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B10" t="n">
-        <v>57862</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R10" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,11 +1538,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1569,32 +1564,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B11" t="n">
-        <v>80228</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1604,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R11" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,6 +1635,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1669,7 +1669,7 @@
         <v>129920250</v>
       </c>
       <c r="B12" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129920258</v>
       </c>
       <c r="B13" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>129920252</v>
       </c>
       <c r="B14" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129920255</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129920263</v>
       </c>
       <c r="B3" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>129920247</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>129920256</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129920249</v>
       </c>
       <c r="B6" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129920260</v>
+        <v>129920246</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>91776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>729692</v>
+        <v>729791</v>
       </c>
       <c r="R7" t="n">
-        <v>7122773</v>
+        <v>7122551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,11 +1237,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,10 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129920246</v>
+        <v>129920260</v>
       </c>
       <c r="B8" t="n">
-        <v>91775</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>729791</v>
+        <v>729692</v>
       </c>
       <c r="R8" t="n">
-        <v>7122551</v>
+        <v>7122773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1334,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1368,7 +1368,7 @@
         <v>129920254</v>
       </c>
       <c r="B9" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129920248</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>129920261</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>129920250</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129920258</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>129920252</v>
       </c>
       <c r="B14" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>80230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R5" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,11 +1038,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B6" t="n">
-        <v>80230</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1104,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R6" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1140,6 +1135,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 55941-2025 artfynd.xlsx
+++ b/artfynd/A 55941-2025 artfynd.xlsx
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129920249</v>
+        <v>129920256</v>
       </c>
       <c r="B5" t="n">
-        <v>80230</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729726</v>
+        <v>729688</v>
       </c>
       <c r="R5" t="n">
-        <v>7122755</v>
+        <v>7122792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,6 +1038,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,32 +1069,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129920256</v>
+        <v>129920249</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>80230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729688</v>
+        <v>729726</v>
       </c>
       <c r="R6" t="n">
-        <v>7122792</v>
+        <v>7122755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1135,11 +1140,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129920248</v>
+        <v>129920261</v>
       </c>
       <c r="B10" t="n">
-        <v>80230</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729725</v>
+        <v>729692</v>
       </c>
       <c r="R10" t="n">
-        <v>7122755</v>
+        <v>7122525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1538,6 +1538,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,32 +1569,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129920261</v>
+        <v>129920248</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>80230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729692</v>
+        <v>729725</v>
       </c>
       <c r="R11" t="n">
-        <v>7122525</v>
+        <v>7122755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1635,11 +1640,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
